--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="49">
   <si>
     <t>Test ID</t>
   </si>
@@ -22,190 +22,142 @@
     <t>Test Name</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Execution Time (ms)</t>
+  </si>
+  <si>
     <t>Priority</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Execution Time (ms)</t>
-  </si>
-  <si>
-    <t>Failure Reason</t>
-  </si>
-  <si>
-    <t>TC_AUTH_035</t>
+    <t>SEL_AUTH_033</t>
   </si>
   <si>
     <t>Authentication</t>
   </si>
   <si>
-    <t>Authentication - Test Scenario 35</t>
+    <t>Authentication - Live Web Scenario 33</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>SEL_AUTHZ_026</t>
+  </si>
+  <si>
+    <t>Authorization</t>
+  </si>
+  <si>
+    <t>Authorization - Live Web Scenario 26</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>SEL_NAV_019</t>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>Navigation - Live Web Scenario 19</t>
+  </si>
+  <si>
+    <t>SEL_UIV_022</t>
+  </si>
+  <si>
+    <t>UI Validation</t>
+  </si>
+  <si>
+    <t>UI Validation - Live Web Scenario 22</t>
+  </si>
+  <si>
+    <t>SEL_FORM_005</t>
+  </si>
+  <si>
+    <t>Forms</t>
+  </si>
+  <si>
+    <t>Forms - Live Web Scenario 5</t>
   </si>
   <si>
     <t>P3</t>
   </si>
   <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>Element not found or validation timeout on Authentication screen.</t>
-  </si>
-  <si>
-    <t>TC_AUTHZ_030</t>
-  </si>
-  <si>
-    <t>Authorization</t>
-  </si>
-  <si>
-    <t>Authorization - Test Scenario 30</t>
-  </si>
-  <si>
-    <t>Element not found or validation timeout on Authorization screen.</t>
-  </si>
-  <si>
-    <t>TC_PROF_015</t>
-  </si>
-  <si>
-    <t>Profile Management</t>
-  </si>
-  <si>
-    <t>Profile Management - Test Scenario 15</t>
-  </si>
-  <si>
-    <t>Element not found or validation timeout on Profile Management screen.</t>
-  </si>
-  <si>
-    <t>TC_NAV_030</t>
-  </si>
-  <si>
-    <t>Navigation</t>
-  </si>
-  <si>
-    <t>Navigation - Test Scenario 30</t>
-  </si>
-  <si>
-    <t>Element not found or validation timeout on Navigation screen.</t>
-  </si>
-  <si>
-    <t>TC_FORM_015</t>
-  </si>
-  <si>
-    <t>Forms</t>
-  </si>
-  <si>
-    <t>Forms - Test Scenario 15</t>
-  </si>
-  <si>
-    <t>Element not found or validation timeout on Forms screen.</t>
-  </si>
-  <si>
-    <t>TC_CRUD_010</t>
+    <t>SEL_FORM_038</t>
+  </si>
+  <si>
+    <t>Forms - Live Web Scenario 38</t>
+  </si>
+  <si>
+    <t>SEL_CRUD_021</t>
   </si>
   <si>
     <t>CRUD Operations</t>
   </si>
   <si>
-    <t>CRUD Operations - Test Scenario 10</t>
-  </si>
-  <si>
-    <t>Element not found or validation timeout on CRUD Operations screen.</t>
-  </si>
-  <si>
-    <t>TC_SRCH_005</t>
-  </si>
-  <si>
-    <t>Search</t>
-  </si>
-  <si>
-    <t>Search - Test Scenario 5</t>
-  </si>
-  <si>
-    <t>Element not found or validation timeout on Search screen.</t>
-  </si>
-  <si>
-    <t>TC_FLTR_020</t>
-  </si>
-  <si>
-    <t>Filters</t>
-  </si>
-  <si>
-    <t>Filters - Test Scenario 20</t>
-  </si>
-  <si>
-    <t>Element not found or validation timeout on Filters screen.</t>
-  </si>
-  <si>
-    <t>TC_VAL_035</t>
+    <t>CRUD Operations - Live Web Scenario 21</t>
+  </si>
+  <si>
+    <t>SEL_VAL_004</t>
   </si>
   <si>
     <t>Input Validation</t>
   </si>
   <si>
-    <t>Input Validation - Test Scenario 35</t>
-  </si>
-  <si>
-    <t>Element not found or validation timeout on Input Validation screen.</t>
-  </si>
-  <si>
-    <t>TC_SESS_010</t>
+    <t>Input Validation - Live Web Scenario 4</t>
+  </si>
+  <si>
+    <t>SEL_VAL_037</t>
+  </si>
+  <si>
+    <t>Input Validation - Live Web Scenario 37</t>
+  </si>
+  <si>
+    <t>SEL_SESS_010</t>
   </si>
   <si>
     <t>Session Management</t>
   </si>
   <si>
-    <t>Session Management - Test Scenario 10</t>
-  </si>
-  <si>
-    <t>Element not found or validation timeout on Session Management screen.</t>
-  </si>
-  <si>
-    <t>TC_UPLD_005</t>
-  </si>
-  <si>
-    <t>File Upload</t>
-  </si>
-  <si>
-    <t>File Upload - Test Scenario 5</t>
-  </si>
-  <si>
-    <t>Element not found or validation timeout on File Upload screen.</t>
-  </si>
-  <si>
-    <t>TC_ACC_010</t>
+    <t>Session Management - Live Web Scenario 10</t>
+  </si>
+  <si>
+    <t>SEL_ACC_003</t>
   </si>
   <si>
     <t>Accessibility</t>
   </si>
   <si>
-    <t>Accessibility - Test Scenario 10</t>
-  </si>
-  <si>
-    <t>Element not found or validation timeout on Accessibility screen.</t>
-  </si>
-  <si>
-    <t>TC_PERF_015</t>
-  </si>
-  <si>
-    <t>Performance Smoke Tests</t>
-  </si>
-  <si>
-    <t>Performance Smoke Tests - Test Scenario 15</t>
-  </si>
-  <si>
-    <t>Element not found or validation timeout on Performance Smoke Tests screen.</t>
-  </si>
-  <si>
-    <t>TC_REGR_030</t>
-  </si>
-  <si>
-    <t>Regression Suite</t>
-  </si>
-  <si>
-    <t>Regression Suite - Test Scenario 30</t>
-  </si>
-  <si>
-    <t>Element not found or validation timeout on Regression Suite screen.</t>
+    <t>Accessibility - Live Web Scenario 3</t>
+  </si>
+  <si>
+    <t>SEL_RESP_016</t>
+  </si>
+  <si>
+    <t>Responsive Design</t>
+  </si>
+  <si>
+    <t>Responsive Design - Live Web Scenario 16</t>
+  </si>
+  <si>
+    <t>SEL_REGR_009</t>
+  </si>
+  <si>
+    <t>Regression</t>
+  </si>
+  <si>
+    <t>Regression - Live Web Scenario 9</t>
+  </si>
+  <si>
+    <t>SEL_REGR_042</t>
+  </si>
+  <si>
+    <t>Regression - Live Web Scenario 42</t>
   </si>
 </sst>
 </file>
@@ -238,7 +190,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="10B981"/>
+        <fgColor rgb="2563EB"/>
       </patternFill>
     </fill>
   </fills>
@@ -597,19 +549,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="45" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -628,330 +579,285 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>504</v>
+      </c>
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="F2">
-        <v>507</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>517</v>
+      </c>
+      <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4">
+        <v>511</v>
+      </c>
+      <c r="F4" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5">
+        <v>512</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>513</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>508</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8">
         <v>503</v>
       </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9">
+        <v>515</v>
+      </c>
+      <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4">
-        <v>514</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10">
+        <v>509</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11">
+        <v>509</v>
+      </c>
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12">
+        <v>517</v>
+      </c>
+      <c r="F12" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5">
-        <v>502</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13">
+        <v>504</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14">
+        <v>503</v>
+      </c>
+      <c r="F14" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>508</v>
-      </c>
-      <c r="G6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15">
         <v>509</v>
       </c>
-      <c r="G7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8">
-        <v>512</v>
-      </c>
-      <c r="G8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9">
-        <v>508</v>
-      </c>
-      <c r="G9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10">
-        <v>505</v>
-      </c>
-      <c r="G10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11">
-        <v>508</v>
-      </c>
-      <c r="G11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12">
-        <v>502</v>
-      </c>
-      <c r="G12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13">
-        <v>508</v>
-      </c>
-      <c r="G13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14">
-        <v>503</v>
-      </c>
-      <c r="G14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15">
-        <v>508</v>
-      </c>
-      <c r="G15" t="s">
-        <v>64</v>
+      <c r="F15" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
